--- a/data/Experiment/Raw/Spreadsheets/TheWorks_07232025.xlsx
+++ b/data/Experiment/Raw/Spreadsheets/TheWorks_07232025.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fernbromley/Desktop/SeedlingMortality/data/Experiment/Raw/Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7276AEF-B8D0-C042-A66D-1501D92675CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84588C68-7D32-5E40-A4DB-E0BF591004FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10020" yWindow="760" windowWidth="19380" windowHeight="17120" activeTab="1" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
+    <workbookView xWindow="10020" yWindow="760" windowWidth="10000" windowHeight="17120" xr2:uid="{CA551DF1-0ED1-674A-8F89-05216640288A}"/>
   </bookViews>
   <sheets>
     <sheet name="PIPO" sheetId="1" r:id="rId1"/>
     <sheet name="PSME" sheetId="3" r:id="rId2"/>
-    <sheet name="PIFL" sheetId="2" r:id="rId3"/>
-    <sheet name="PIEN" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="124">
   <si>
     <t>PIPO1</t>
   </si>
@@ -233,186 +231,6 @@
     <t>PIPO60</t>
   </si>
   <si>
-    <t>PIFL1</t>
-  </si>
-  <si>
-    <t>PIFL2</t>
-  </si>
-  <si>
-    <t>PIFL3</t>
-  </si>
-  <si>
-    <t>PIFL4</t>
-  </si>
-  <si>
-    <t>PIFL5</t>
-  </si>
-  <si>
-    <t>PIFL6</t>
-  </si>
-  <si>
-    <t>PIFL7</t>
-  </si>
-  <si>
-    <t>PIFL8</t>
-  </si>
-  <si>
-    <t>PIFL9</t>
-  </si>
-  <si>
-    <t>PIFL10</t>
-  </si>
-  <si>
-    <t>PIFL11</t>
-  </si>
-  <si>
-    <t>PIFL12</t>
-  </si>
-  <si>
-    <t>PIFL13</t>
-  </si>
-  <si>
-    <t>PIFL14</t>
-  </si>
-  <si>
-    <t>PIFL15</t>
-  </si>
-  <si>
-    <t>PIFL16</t>
-  </si>
-  <si>
-    <t>PIFL17</t>
-  </si>
-  <si>
-    <t>PIFL18</t>
-  </si>
-  <si>
-    <t>PIFL19</t>
-  </si>
-  <si>
-    <t>PIFL20</t>
-  </si>
-  <si>
-    <t>PIFL21</t>
-  </si>
-  <si>
-    <t>PIFL22</t>
-  </si>
-  <si>
-    <t>PIFL23</t>
-  </si>
-  <si>
-    <t>PIFL24</t>
-  </si>
-  <si>
-    <t>PIFL25</t>
-  </si>
-  <si>
-    <t>PIFL26</t>
-  </si>
-  <si>
-    <t>PIFL27</t>
-  </si>
-  <si>
-    <t>PIFL28</t>
-  </si>
-  <si>
-    <t>PIFL29</t>
-  </si>
-  <si>
-    <t>PIFL30</t>
-  </si>
-  <si>
-    <t>PIFL31</t>
-  </si>
-  <si>
-    <t>PIFL32</t>
-  </si>
-  <si>
-    <t>PIFL33</t>
-  </si>
-  <si>
-    <t>PIFL34</t>
-  </si>
-  <si>
-    <t>PIFL35</t>
-  </si>
-  <si>
-    <t>PIFL36</t>
-  </si>
-  <si>
-    <t>PIFL37</t>
-  </si>
-  <si>
-    <t>PIFL38</t>
-  </si>
-  <si>
-    <t>PIFL39</t>
-  </si>
-  <si>
-    <t>PIFL40</t>
-  </si>
-  <si>
-    <t>PIFL41</t>
-  </si>
-  <si>
-    <t>PIFL42</t>
-  </si>
-  <si>
-    <t>PIFL43</t>
-  </si>
-  <si>
-    <t>PIFL44</t>
-  </si>
-  <si>
-    <t>PIFL45</t>
-  </si>
-  <si>
-    <t>PIFL46</t>
-  </si>
-  <si>
-    <t>PIFL47</t>
-  </si>
-  <si>
-    <t>PIFL48</t>
-  </si>
-  <si>
-    <t>PIFL49</t>
-  </si>
-  <si>
-    <t>PIFL50</t>
-  </si>
-  <si>
-    <t>PIFL51</t>
-  </si>
-  <si>
-    <t>PIFL52</t>
-  </si>
-  <si>
-    <t>PIFL53</t>
-  </si>
-  <si>
-    <t>PIFL54</t>
-  </si>
-  <si>
-    <t>PIFL55</t>
-  </si>
-  <si>
-    <t>PIFL56</t>
-  </si>
-  <si>
-    <t>PIFL57</t>
-  </si>
-  <si>
-    <t>PIFL58</t>
-  </si>
-  <si>
-    <t>PIFL59</t>
-  </si>
-  <si>
-    <t>PIFL60</t>
-  </si>
-  <si>
     <t>PSME1</t>
   </si>
   <si>
@@ -591,186 +409,6 @@
   </si>
   <si>
     <t>PSME60</t>
-  </si>
-  <si>
-    <t>PIEN1</t>
-  </si>
-  <si>
-    <t>PIEN2</t>
-  </si>
-  <si>
-    <t>PIEN3</t>
-  </si>
-  <si>
-    <t>PIEN4</t>
-  </si>
-  <si>
-    <t>PIEN5</t>
-  </si>
-  <si>
-    <t>PIEN6</t>
-  </si>
-  <si>
-    <t>PIEN7</t>
-  </si>
-  <si>
-    <t>PIEN8</t>
-  </si>
-  <si>
-    <t>PIEN9</t>
-  </si>
-  <si>
-    <t>PIEN10</t>
-  </si>
-  <si>
-    <t>PIEN11</t>
-  </si>
-  <si>
-    <t>PIEN12</t>
-  </si>
-  <si>
-    <t>PIEN13</t>
-  </si>
-  <si>
-    <t>PIEN14</t>
-  </si>
-  <si>
-    <t>PIEN15</t>
-  </si>
-  <si>
-    <t>PIEN16</t>
-  </si>
-  <si>
-    <t>PIEN17</t>
-  </si>
-  <si>
-    <t>PIEN18</t>
-  </si>
-  <si>
-    <t>PIEN19</t>
-  </si>
-  <si>
-    <t>PIEN20</t>
-  </si>
-  <si>
-    <t>PIEN21</t>
-  </si>
-  <si>
-    <t>PIEN22</t>
-  </si>
-  <si>
-    <t>PIEN23</t>
-  </si>
-  <si>
-    <t>PIEN24</t>
-  </si>
-  <si>
-    <t>PIEN25</t>
-  </si>
-  <si>
-    <t>PIEN26</t>
-  </si>
-  <si>
-    <t>PIEN27</t>
-  </si>
-  <si>
-    <t>PIEN28</t>
-  </si>
-  <si>
-    <t>PIEN29</t>
-  </si>
-  <si>
-    <t>PIEN30</t>
-  </si>
-  <si>
-    <t>PIEN31</t>
-  </si>
-  <si>
-    <t>PIEN32</t>
-  </si>
-  <si>
-    <t>PIEN33</t>
-  </si>
-  <si>
-    <t>PIEN34</t>
-  </si>
-  <si>
-    <t>PIEN35</t>
-  </si>
-  <si>
-    <t>PIEN36</t>
-  </si>
-  <si>
-    <t>PIEN37</t>
-  </si>
-  <si>
-    <t>PIEN38</t>
-  </si>
-  <si>
-    <t>PIEN39</t>
-  </si>
-  <si>
-    <t>PIEN40</t>
-  </si>
-  <si>
-    <t>PIEN41</t>
-  </si>
-  <si>
-    <t>PIEN42</t>
-  </si>
-  <si>
-    <t>PIEN43</t>
-  </si>
-  <si>
-    <t>PIEN44</t>
-  </si>
-  <si>
-    <t>PIEN45</t>
-  </si>
-  <si>
-    <t>PIEN46</t>
-  </si>
-  <si>
-    <t>PIEN47</t>
-  </si>
-  <si>
-    <t>PIEN48</t>
-  </si>
-  <si>
-    <t>PIEN49</t>
-  </si>
-  <si>
-    <t>PIEN50</t>
-  </si>
-  <si>
-    <t>PIEN51</t>
-  </si>
-  <si>
-    <t>PIEN52</t>
-  </si>
-  <si>
-    <t>PIEN53</t>
-  </si>
-  <si>
-    <t>PIEN54</t>
-  </si>
-  <si>
-    <t>PIEN55</t>
-  </si>
-  <si>
-    <t>PIEN56</t>
-  </si>
-  <si>
-    <t>PIEN57</t>
-  </si>
-  <si>
-    <t>PIEN58</t>
-  </si>
-  <si>
-    <t>PIEN59</t>
-  </si>
-  <si>
-    <t>PIEN60</t>
   </si>
 </sst>
 </file>
@@ -2068,7 +1706,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="B2">
         <v>491.3</v>
@@ -2082,7 +1720,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>505.4</v>
@@ -2096,7 +1734,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>514.70000000000005</v>
@@ -2110,7 +1748,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <v>478</v>
@@ -2124,7 +1762,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>501.4</v>
@@ -2138,7 +1776,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>496.4</v>
@@ -2152,7 +1790,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="B8">
         <v>507.7</v>
@@ -2166,7 +1804,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <v>503.6</v>
@@ -2180,7 +1818,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <v>510.4</v>
@@ -2194,7 +1832,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="B11">
         <v>464.1</v>
@@ -2208,7 +1846,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="B12">
         <v>499.2</v>
@@ -2222,7 +1860,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="B13">
         <v>500.7</v>
@@ -2236,7 +1874,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="B14">
         <v>517.20000000000005</v>
@@ -2250,7 +1888,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="B15">
         <v>505</v>
@@ -2264,7 +1902,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="B16">
         <v>479.9</v>
@@ -2278,7 +1916,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="B17">
         <v>490.7</v>
@@ -2292,7 +1930,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="B18">
         <v>497.2</v>
@@ -2306,7 +1944,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="B19">
         <v>519.4</v>
@@ -2320,7 +1958,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="B20">
         <v>517.4</v>
@@ -2334,7 +1972,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="B21">
         <v>491.8</v>
@@ -2348,7 +1986,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="B22">
         <v>489.1</v>
@@ -2362,7 +2000,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="B23">
         <v>528.70000000000005</v>
@@ -2376,7 +2014,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="B24">
         <v>495.7</v>
@@ -2390,7 +2028,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="B25">
         <v>499.2</v>
@@ -2404,7 +2042,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="B26">
         <v>474.3</v>
@@ -2418,7 +2056,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="B27">
         <v>414.9</v>
@@ -2432,7 +2070,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="B28">
         <v>509.1</v>
@@ -2446,7 +2084,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="B29">
         <v>475.7</v>
@@ -2460,7 +2098,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="B30">
         <v>514.20000000000005</v>
@@ -2474,7 +2112,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="B31">
         <v>477.4</v>
@@ -2488,7 +2126,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="B32">
         <v>470.1</v>
@@ -2502,7 +2140,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="B33">
         <v>487.3</v>
@@ -2516,7 +2154,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="B34">
         <v>503.4</v>
@@ -2530,7 +2168,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="B35">
         <v>496</v>
@@ -2544,7 +2182,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="B36">
         <v>484.8</v>
@@ -2558,7 +2196,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="B37">
         <v>482.6</v>
@@ -2572,7 +2210,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="B38">
         <v>463.4</v>
@@ -2586,7 +2224,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="B39">
         <v>504.1</v>
@@ -2600,7 +2238,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="B40">
         <v>489.9</v>
@@ -2614,7 +2252,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="B41">
         <v>458</v>
@@ -2628,7 +2266,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="B42">
         <v>457.8</v>
@@ -2642,7 +2280,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="B43">
         <v>477.8</v>
@@ -2656,7 +2294,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="B44">
         <v>447.4</v>
@@ -2670,7 +2308,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="B45">
         <v>414.7</v>
@@ -2684,7 +2322,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="B46">
         <v>477.6</v>
@@ -2698,7 +2336,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="B47">
         <v>489.2</v>
@@ -2712,7 +2350,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="B48">
         <v>387.8</v>
@@ -2726,7 +2364,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="B49">
         <v>496</v>
@@ -2740,7 +2378,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="B50">
         <v>457.2</v>
@@ -2754,7 +2392,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="B51">
         <v>421.2</v>
@@ -2768,7 +2406,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="B52">
         <v>499</v>
@@ -2782,7 +2420,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="B53">
         <v>503.5</v>
@@ -2796,7 +2434,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="B54">
         <v>491</v>
@@ -2810,7 +2448,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="B55">
         <v>487.5</v>
@@ -2824,7 +2462,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="B56">
         <v>474.7</v>
@@ -2838,7 +2476,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="B57">
         <v>465</v>
@@ -2852,7 +2490,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="B58">
         <v>504.1</v>
@@ -2866,7 +2504,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="B59">
         <v>498.8</v>
@@ -2880,7 +2518,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="B60">
         <v>479.8</v>
@@ -2894,7 +2532,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="B61">
         <v>497.3</v>
@@ -2914,670 +2552,4 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B18CAA-D5E2-8F4D-8617-88F8364D5DB9}">
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C2:C31" xr:uid="{24150C35-6868-1E47-87A8-3465DD07C9B2}">
-      <formula1>"10%, 25%, 50%, 75%, 90%"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115E6809-C6E9-4B42-AF0B-D16D811C3B7F}">
-  <dimension ref="A1:D61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C2:C31" xr:uid="{CE406483-11A2-DA4E-A178-D21B4EA2E84A}">
-      <formula1>"10%, 25%, 50%, 75%, 90%"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>